--- a/data/merged/2026-09-23/MERGED_UK_Spot-Cleaner_2026-09-23.xlsx
+++ b/data/merged/2026-09-23/MERGED_UK_Spot-Cleaner_2026-09-23.xlsx
@@ -3735,13 +3735,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3911,13 +3911,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -3961,7 +3961,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4005,7 +4005,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4131,13 +4131,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4175,13 +4175,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4533,7 +4533,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4577,7 +4577,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4879,13 +4879,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4923,13 +4923,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4967,13 +4967,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5055,13 +5055,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5231,13 +5231,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5281,7 +5281,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -5363,7 +5363,7 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
@@ -5430,94 +5430,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -5859,7 +5771,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -7132,7 +7044,7 @@
       <c r="B10" s="13"/>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B07CH4WZJ9</t>
         </is>
       </c>
       <c r="D10" s="14"/>
@@ -7145,23 +7057,23 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Oxygen Boost Formula Booster for SpotClean 1L 1134NsA cleaning solution booster for use on carpet, upholstery, area</t>
+          <t>BISSELL SpotClean ProHeat Portable Spot Cleaner 330W 36981sUpholstery cleaner with HeatWave Technology, removes stains from</t>
         </is>
       </c>
       <c r="I10" s="14"/>
       <c r="J10" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0753NXDPR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B07CH4WZJ9?psc=1</t>
         </is>
       </c>
       <c r="K10" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/51-YKuNNnoL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61cy6Zl-hUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L10" s="14" t="inlineStr">
         <is>
-          <t>B0753NXDPR</t>
+          <t>B07CH4WZJ9</t>
         </is>
       </c>
       <c r="M10" s="1"/>
@@ -7177,16 +7089,18 @@
       <c r="W10" s="15"/>
       <c r="X10" s="15"/>
       <c r="Y10"/>
-      <c r="Z10" s="19"/>
+      <c r="Z10" s="19">
+        <v>82.5</v>
+      </c>
       <c r="AA10"/>
       <c r="AB10"/>
       <c r="AC10"/>
       <c r="AD10" s="20">
-        <v>9397</v>
+        <v>5257</v>
       </c>
       <c r="AE10"/>
       <c r="AF10" s="21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG10" s="22">
         <v>0</v>
@@ -7238,7 +7152,7 @@
       <c r="B11" s="13"/>
       <c r="C11" s="14" t="inlineStr">
         <is>
-          <t>B07CH4WZJ9</t>
+          <t>B07MWDYH1F</t>
         </is>
       </c>
       <c r="D11" s="14"/>
@@ -7251,23 +7165,23 @@
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean ProHeat Portable Spot Cleaner 330W 36981sUpholstery cleaner with HeatWave Technology, removes stains from</t>
+          <t>Vax Compact Power Upright Upholstery &amp; Carpet Cleaner Machine CWCPV011sUpright shampooer washer for spills, stains, rugs &amp;</t>
         </is>
       </c>
       <c r="I11" s="14"/>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B07CH4WZJ9?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B07MWDYH1F?psc=1</t>
         </is>
       </c>
       <c r="K11" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61cy6Zl-hUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61hzbjuSlWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
-          <t>B07CH4WZJ9</t>
+          <t>B07MWDYH1F</t>
         </is>
       </c>
       <c r="M11" s="1"/>
@@ -7283,14 +7197,12 @@
       <c r="W11" s="15"/>
       <c r="X11" s="15"/>
       <c r="Y11"/>
-      <c r="Z11" s="19">
-        <v>82.5</v>
-      </c>
+      <c r="Z11" s="19"/>
       <c r="AA11"/>
       <c r="AB11"/>
       <c r="AC11"/>
       <c r="AD11" s="20">
-        <v>5257</v>
+        <v>7433</v>
       </c>
       <c r="AE11"/>
       <c r="AF11" s="21">
@@ -7346,7 +7258,7 @@
       <c r="B12" s="13"/>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>B07MWDYH1F</t>
+          <t>B08XK5C5TT</t>
         </is>
       </c>
       <c r="D12" s="14"/>
@@ -7359,23 +7271,23 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Vax Compact Power Upright Upholstery &amp; Carpet Cleaner Machine CWCPV011sUpright shampooer washer for spills, stains, rugs &amp;</t>
+          <t>Vax Platinum SmartWash Upright Carpet &amp; Upholstery Cleaner CDCW-SWXSsShampooer machine, stain &amp; odour removal for rugs &amp; so</t>
         </is>
       </c>
       <c r="I12" s="14"/>
       <c r="J12" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B07MWDYH1F?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B08XK5C5TT?psc=1</t>
         </is>
       </c>
       <c r="K12" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61hzbjuSlWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7141egivyQL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>B07MWDYH1F</t>
+          <t>B08XK5C5TT</t>
         </is>
       </c>
       <c r="M12" s="1"/>
@@ -7396,11 +7308,11 @@
       <c r="AB12"/>
       <c r="AC12"/>
       <c r="AD12" s="20">
-        <v>7433</v>
+        <v>2777</v>
       </c>
       <c r="AE12"/>
       <c r="AF12" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG12" s="22">
         <v>0</v>
@@ -7452,7 +7364,7 @@
       <c r="B13" s="13"/>
       <c r="C13" s="14" t="inlineStr">
         <is>
-          <t>B08XK5C5TT</t>
+          <t>B09RZDRFPP</t>
         </is>
       </c>
       <c r="D13" s="14"/>
@@ -7465,23 +7377,23 @@
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Vax Platinum SmartWash Upright Carpet &amp; Upholstery Cleaner CDCW-SWXSsShampooer machine, stain &amp; odour removal for rugs &amp; so</t>
+          <t>Vax SpotWash Home Duo Carpet &amp; Furniture Spot Cleaner CDSW-MPXPsPortable upholstery cleaner machine, deep cleaning for spil</t>
         </is>
       </c>
       <c r="I13" s="14"/>
       <c r="J13" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B08XK5C5TT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09RZDRFPP?psc=1</t>
         </is>
       </c>
       <c r="K13" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7141egivyQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ofQFCHaWL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
-          <t>B08XK5C5TT</t>
+          <t>B09RZDRFPP</t>
         </is>
       </c>
       <c r="M13" s="1"/>
@@ -7502,11 +7414,11 @@
       <c r="AB13"/>
       <c r="AC13"/>
       <c r="AD13" s="20">
-        <v>2777</v>
+        <v>2691</v>
       </c>
       <c r="AE13"/>
       <c r="AF13" s="21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG13" s="22">
         <v>0</v>
@@ -7558,7 +7470,7 @@
       <c r="B14" s="13"/>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>B09RZDRFPP</t>
+          <t>B09RZPB79W</t>
         </is>
       </c>
       <c r="D14" s="14"/>
@@ -7571,23 +7483,23 @@
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>Vax SpotWash Home Duo Carpet &amp; Furniture Spot Cleaner CDSW-MPXPsPortable upholstery cleaner machine, deep cleaning for spil</t>
+          <t>Vax SpotWash Duo Compact Carpet &amp; Upholstery Spot Cleaner CDCW-CSXAsHandheld carpet cleaner machine for pet messes, furnitu</t>
         </is>
       </c>
       <c r="I14" s="14"/>
       <c r="J14" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09RZDRFPP?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B09RZPB79W?psc=1</t>
         </is>
       </c>
       <c r="K14" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ofQFCHaWL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TTHRPYsjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L14" s="14" t="inlineStr">
         <is>
-          <t>B09RZDRFPP</t>
+          <t>B09RZPB79W</t>
         </is>
       </c>
       <c r="M14" s="1"/>
@@ -7608,7 +7520,7 @@
       <c r="AB14"/>
       <c r="AC14"/>
       <c r="AD14" s="20">
-        <v>2691</v>
+        <v>4800</v>
       </c>
       <c r="AE14"/>
       <c r="AF14" s="21">
@@ -7664,7 +7576,7 @@
       <c r="B15" s="13"/>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>B09RZPB79W</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="D15" s="14"/>
@@ -7677,23 +7589,23 @@
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Vax SpotWash Duo Compact Carpet &amp; Upholstery Spot Cleaner CDCW-CSXAsHandheld carpet cleaner machine for pet messes, furnitu</t>
+          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
         </is>
       </c>
       <c r="I15" s="14"/>
       <c r="J15" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B09RZPB79W?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
         </is>
       </c>
       <c r="K15" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TTHRPYsjL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L15" s="14" t="inlineStr">
         <is>
-          <t>B09RZPB79W</t>
+          <t>B0B4JST7J8</t>
         </is>
       </c>
       <c r="M15" s="1"/>
@@ -7709,16 +7621,18 @@
       <c r="W15" s="15"/>
       <c r="X15" s="15"/>
       <c r="Y15"/>
-      <c r="Z15" s="19"/>
+      <c r="Z15" s="19">
+        <v>33.33</v>
+      </c>
       <c r="AA15"/>
       <c r="AB15"/>
       <c r="AC15"/>
       <c r="AD15" s="20">
-        <v>4800</v>
+        <v>508</v>
       </c>
       <c r="AE15"/>
       <c r="AF15" s="21">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AG15" s="22">
         <v>0</v>
@@ -7770,7 +7684,7 @@
       <c r="B16" s="13"/>
       <c r="C16" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B0B5713JZW</t>
         </is>
       </c>
       <c r="D16" s="14"/>
@@ -7783,23 +7697,23 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Swan TV’s Queen of Clean Handheld Carpet Cleaner with 5m Power Cord, 480ml Water Tank, 500W, Pink, SC18410QOCN</t>
+          <t>Vax Dual Power Pet Advance Upright Carpet &amp; Upholstery Cleaner ECR2V1PsRug shampooer washer for pet mess, stairs &amp; sofas, p</t>
         </is>
       </c>
       <c r="I16" s="14"/>
       <c r="J16" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0B5713JZW?psc=1</t>
         </is>
       </c>
       <c r="K16" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71kt5MoDO9L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>B0B4JST7J8</t>
+          <t>B0B5713JZW</t>
         </is>
       </c>
       <c r="M16" s="1"/>
@@ -7815,18 +7729,16 @@
       <c r="W16" s="15"/>
       <c r="X16" s="15"/>
       <c r="Y16"/>
-      <c r="Z16" s="19">
-        <v>33.33</v>
-      </c>
+      <c r="Z16" s="19"/>
       <c r="AA16"/>
       <c r="AB16"/>
       <c r="AC16"/>
       <c r="AD16" s="20">
-        <v>508</v>
+        <v>6295</v>
       </c>
       <c r="AE16"/>
       <c r="AF16" s="21">
-        <v>3.8</v>
+        <v>4.3</v>
       </c>
       <c r="AG16" s="22">
         <v>0</v>
@@ -7878,7 +7790,7 @@
       <c r="B17" s="13"/>
       <c r="C17" s="14" t="inlineStr">
         <is>
-          <t>B0B5713JZW</t>
+          <t>B0BX3CS1MS</t>
         </is>
       </c>
       <c r="D17" s="14"/>
@@ -7891,23 +7803,23 @@
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Vax Dual Power Pet Advance Upright Carpet &amp; Upholstery Cleaner ECR2V1PsRug shampooer washer for pet mess, stairs &amp; sofas, p</t>
+          <t>Rug Doctor TRUDeep Carpet Cleaner (1300W)s30% More Suction - TruDeep Dual Brush Technology – Faster Drying - Deeper Stain &amp;</t>
         </is>
       </c>
       <c r="I17" s="14"/>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0B5713JZW?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0BX3CS1MS?psc=1</t>
         </is>
       </c>
       <c r="K17" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71kt5MoDO9L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81gIVoIFeGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>B0B5713JZW</t>
+          <t>B0BX3CS1MS</t>
         </is>
       </c>
       <c r="M17" s="1"/>
@@ -7928,11 +7840,11 @@
       <c r="AB17"/>
       <c r="AC17"/>
       <c r="AD17" s="20">
-        <v>6295</v>
+        <v>120</v>
       </c>
       <c r="AE17"/>
       <c r="AF17" s="21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG17" s="22">
         <v>0</v>
@@ -7984,7 +7896,7 @@
       <c r="B18" s="13"/>
       <c r="C18" s="14" t="inlineStr">
         <is>
-          <t>B0BX3CS1MS</t>
+          <t>B0CFV7HZHH</t>
         </is>
       </c>
       <c r="D18" s="14"/>
@@ -7997,23 +7909,23 @@
       </c>
       <c r="H18" s="14" t="inlineStr">
         <is>
-          <t>Rug Doctor TRUDeep Carpet Cleaner (1300W)s30% More Suction - TruDeep Dual Brush Technology – Faster Drying - Deeper Stain &amp;</t>
+          <t>Shark StainStriker Stain and Spot Cleaner, Blue PX200UK, 2 Tools, PX200UKsCompact Carpet and Upholstery Cleaner with Powerf</t>
         </is>
       </c>
       <c r="I18" s="14"/>
       <c r="J18" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0BX3CS1MS?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1</t>
         </is>
       </c>
       <c r="K18" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81gIVoIFeGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L18" s="14" t="inlineStr">
         <is>
-          <t>B0BX3CS1MS</t>
+          <t>B0CFV7HZHH</t>
         </is>
       </c>
       <c r="M18" s="1"/>
@@ -8034,11 +7946,11 @@
       <c r="AB18"/>
       <c r="AC18"/>
       <c r="AD18" s="20">
-        <v>120</v>
+        <v>278</v>
       </c>
       <c r="AE18"/>
       <c r="AF18" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG18" s="22">
         <v>0</v>
@@ -8090,7 +8002,7 @@
       <c r="B19" s="13"/>
       <c r="C19" s="14" t="inlineStr">
         <is>
-          <t>B0CFV7HZHH</t>
+          <t>B0CHYQ4NMS</t>
         </is>
       </c>
       <c r="D19" s="14"/>
@@ -8103,23 +8015,23 @@
       </c>
       <c r="H19" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker Stain and Spot Cleaner, Blue PX200UK, 2 Tools, PX200UKsCompact Carpet and Upholstery Cleaner with Powerf</t>
+          <t>BISSELL Revolution HydroSteam Upright Carpet Cleaner 3670EsRemoves stains with HydroSteam™ Technology, carpets dry in 30 mi</t>
         </is>
       </c>
       <c r="I19" s="14"/>
       <c r="J19" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CHYQ4NMS?psc=1</t>
         </is>
       </c>
       <c r="K19" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61ae2raT2BL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L19" s="14" t="inlineStr">
         <is>
-          <t>B0CFV7HZHH</t>
+          <t>B0CHYQ4NMS</t>
         </is>
       </c>
       <c r="M19" s="1"/>
@@ -8140,11 +8052,11 @@
       <c r="AB19"/>
       <c r="AC19"/>
       <c r="AD19" s="20">
-        <v>278</v>
+        <v>96</v>
       </c>
       <c r="AE19"/>
       <c r="AF19" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG19" s="22">
         <v>0</v>
@@ -8196,7 +8108,7 @@
       <c r="B20" s="13"/>
       <c r="C20" s="14" t="inlineStr">
         <is>
-          <t>B0CHYQ4NMS</t>
+          <t>B0CND95KY4</t>
         </is>
       </c>
       <c r="D20" s="14"/>
@@ -8209,23 +8121,23 @@
       </c>
       <c r="H20" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Revolution HydroSteam Upright Carpet Cleaner 3670EsRemoves stains with HydroSteam™ Technology, carpets dry in 30 mi</t>
+          <t>Vytronix SWASH450P Spot &amp; Stain Cleaner for Carpet, Upholstery &amp; Car Seats – Powerful 450W Portable Spot Washer with Self-Cle</t>
         </is>
       </c>
       <c r="I20" s="14"/>
       <c r="J20" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CHYQ4NMS?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CND95KY4?psc=1</t>
         </is>
       </c>
       <c r="K20" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61ae2raT2BL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71PuJ8C+JUL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L20" s="14" t="inlineStr">
         <is>
-          <t>B0CHYQ4NMS</t>
+          <t>B0CND95KY4</t>
         </is>
       </c>
       <c r="M20" s="1"/>
@@ -8246,11 +8158,11 @@
       <c r="AB20"/>
       <c r="AC20"/>
       <c r="AD20" s="20">
-        <v>96</v>
+        <v>2482</v>
       </c>
       <c r="AE20"/>
       <c r="AF20" s="21">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AG20" s="22">
         <v>0</v>
@@ -8302,7 +8214,7 @@
       <c r="B21" s="13"/>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>B0CND95KY4</t>
+          <t>B0CW1QQF4F</t>
         </is>
       </c>
       <c r="D21" s="14"/>
@@ -8315,23 +8227,23 @@
       </c>
       <c r="H21" s="14" t="inlineStr">
         <is>
-          <t>Vytronix SWASH450P Spot &amp; Stain Cleaner for Carpet, Upholstery &amp; Car Seats – Powerful 450W Portable Spot Washer with Self-Cle</t>
+          <t>Vax Platinum Powermax Pet-Design Carpet &amp; Upholstery Cleaner CDCW-PMXPsUpright carpet shampooer for pet mess, stairs, sofas</t>
         </is>
       </c>
       <c r="I21" s="14"/>
       <c r="J21" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CND95KY4?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CW1QQF4F?psc=1</t>
         </is>
       </c>
       <c r="K21" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71PuJ8C+JUL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61W-FhLaf+L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L21" s="14" t="inlineStr">
         <is>
-          <t>B0CND95KY4</t>
+          <t>B0CW1QQF4F</t>
         </is>
       </c>
       <c r="M21" s="1"/>
@@ -8352,11 +8264,11 @@
       <c r="AB21"/>
       <c r="AC21"/>
       <c r="AD21" s="20">
-        <v>2482</v>
+        <v>364</v>
       </c>
       <c r="AE21"/>
       <c r="AF21" s="21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG21" s="22">
         <v>0</v>
@@ -8408,7 +8320,7 @@
       <c r="B22" s="13"/>
       <c r="C22" s="14" t="inlineStr">
         <is>
-          <t>B0CW1QQF4F</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="D22" s="14"/>
@@ -8421,23 +8333,23 @@
       </c>
       <c r="H22" s="14" t="inlineStr">
         <is>
-          <t>Vax Platinum Powermax Pet-Design Carpet &amp; Upholstery Cleaner CDCW-PMXPsUpright carpet shampooer for pet mess, stairs, sofas</t>
+          <t>Daewoo Stairmaster Corded Spotwasher</t>
         </is>
       </c>
       <c r="I22" s="14"/>
       <c r="J22" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CW1QQF4F?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
         </is>
       </c>
       <c r="K22" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61W-FhLaf+L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L22" s="14" t="inlineStr">
         <is>
-          <t>B0CW1QQF4F</t>
+          <t>B0CZRYCLNT</t>
         </is>
       </c>
       <c r="M22" s="1"/>
@@ -8453,16 +8365,18 @@
       <c r="W22" s="15"/>
       <c r="X22" s="15"/>
       <c r="Y22"/>
-      <c r="Z22" s="19"/>
+      <c r="Z22" s="19">
+        <v>41.64</v>
+      </c>
       <c r="AA22"/>
       <c r="AB22"/>
       <c r="AC22"/>
       <c r="AD22" s="20">
-        <v>364</v>
+        <v>316</v>
       </c>
       <c r="AE22"/>
       <c r="AF22" s="21">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="AG22" s="22">
         <v>0</v>
@@ -8514,7 +8428,7 @@
       <c r="B23" s="13"/>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B0D2LLN3GT</t>
         </is>
       </c>
       <c r="D23" s="14"/>
@@ -8527,23 +8441,23 @@
       </c>
       <c r="H23" s="14" t="inlineStr">
         <is>
-          <t>Daewoo Stairmaster Corded Spotwasher</t>
+          <t>Shark StainStriker Stain &amp; Spot Cleaner, PX200UKCPsPortable Carpet &amp; Upholstery Cleaner for Pet Stains, Spills &amp; Deep Clean</t>
         </is>
       </c>
       <c r="I23" s="14"/>
       <c r="J23" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D2LLN3GT?psc=1</t>
         </is>
       </c>
       <c r="K23" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71WxSJgdq2L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L23" s="14" t="inlineStr">
         <is>
-          <t>B0CZRYCLNT</t>
+          <t>B0D2LLN3GT</t>
         </is>
       </c>
       <c r="M23" s="1"/>
@@ -8560,17 +8474,17 @@
       <c r="X23" s="15"/>
       <c r="Y23"/>
       <c r="Z23" s="19">
-        <v>41.64</v>
+        <v>124.99</v>
       </c>
       <c r="AA23"/>
       <c r="AB23"/>
       <c r="AC23"/>
       <c r="AD23" s="20">
-        <v>316</v>
+        <v>380</v>
       </c>
       <c r="AE23"/>
       <c r="AF23" s="21">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG23" s="22">
         <v>0</v>
@@ -8622,7 +8536,7 @@
       <c r="B24" s="13"/>
       <c r="C24" s="14" t="inlineStr">
         <is>
-          <t>B0D2LLN3GT</t>
+          <t>B0D2LNZQ7Y</t>
         </is>
       </c>
       <c r="D24" s="14"/>
@@ -8635,23 +8549,23 @@
       </c>
       <c r="H24" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker Stain &amp; Spot Cleaner, PX200UKCPsPortable Carpet &amp; Upholstery Cleaner for Pet Stains, Spills &amp; Deep Clean</t>
+          <t>Shark CarpetXpert Deep Clean Carpet Cleaner, 2.3L. 960W, Grey, EX150UKCPsBuilt-In Stain &amp; Spot Remover, 3 Tools &amp; Full-Size</t>
         </is>
       </c>
       <c r="I24" s="14"/>
       <c r="J24" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D2LLN3GT?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D2LNZQ7Y?psc=1</t>
         </is>
       </c>
       <c r="K24" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71WxSJgdq2L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/715jhnqP5mL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L24" s="14" t="inlineStr">
         <is>
-          <t>B0D2LLN3GT</t>
+          <t>B0D2LNZQ7Y</t>
         </is>
       </c>
       <c r="M24" s="1"/>
@@ -8667,14 +8581,12 @@
       <c r="W24" s="15"/>
       <c r="X24" s="15"/>
       <c r="Y24"/>
-      <c r="Z24" s="19">
-        <v>124.99</v>
-      </c>
+      <c r="Z24" s="19"/>
       <c r="AA24"/>
       <c r="AB24"/>
       <c r="AC24"/>
       <c r="AD24" s="20">
-        <v>380</v>
+        <v>790</v>
       </c>
       <c r="AE24"/>
       <c r="AF24" s="21">
@@ -8730,7 +8642,7 @@
       <c r="B25" s="13"/>
       <c r="C25" s="14" t="inlineStr">
         <is>
-          <t>B0D2LNZQ7Y</t>
+          <t>B0D6RSDL6X</t>
         </is>
       </c>
       <c r="D25" s="14"/>
@@ -8743,23 +8655,23 @@
       </c>
       <c r="H25" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetXpert Deep Clean Carpet Cleaner, 2.3L. 960W, Grey, EX150UKCPsBuilt-In Stain &amp; Spot Remover, 3 Tools &amp; Full-Size</t>
+          <t>BISSELL Little Green Portable Spot Cleaner &amp; Carpet Stain Remover 4098EsUpholstery and sofa cleaner with powerful suction,</t>
         </is>
       </c>
       <c r="I25" s="14"/>
       <c r="J25" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D2LNZQ7Y?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1</t>
         </is>
       </c>
       <c r="K25" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/715jhnqP5mL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L25" s="14" t="inlineStr">
         <is>
-          <t>B0D2LNZQ7Y</t>
+          <t>B0D6RSDL6X</t>
         </is>
       </c>
       <c r="M25" s="1"/>
@@ -8780,11 +8692,11 @@
       <c r="AB25"/>
       <c r="AC25"/>
       <c r="AD25" s="20">
-        <v>790</v>
+        <v>91844</v>
       </c>
       <c r="AE25"/>
       <c r="AF25" s="21">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AG25" s="22">
         <v>0</v>
@@ -8836,7 +8748,7 @@
       <c r="B26" s="13"/>
       <c r="C26" s="14" t="inlineStr">
         <is>
-          <t>B0D6RSDL6X</t>
+          <t>B0D8154CWN</t>
         </is>
       </c>
       <c r="D26" s="14"/>
@@ -8849,23 +8761,23 @@
       </c>
       <c r="H26" s="14" t="inlineStr">
         <is>
-          <t>BISSELL Little Green Portable Spot Cleaner &amp; Carpet Stain Remover 4098EsUpholstery and sofa cleaner with powerful suction,</t>
+          <t>Vax SpinScrub Power Upright Carpet &amp; Upholstery Cleaner Machine CDCW-SSXSsRug shampooer &amp; handheld spot cleaner, deep stain</t>
         </is>
       </c>
       <c r="I26" s="14"/>
       <c r="J26" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0D8154CWN?psc=1</t>
         </is>
       </c>
       <c r="K26" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/7149mbLCp1L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L26" s="14" t="inlineStr">
         <is>
-          <t>B0D6RSDL6X</t>
+          <t>B0D8154CWN</t>
         </is>
       </c>
       <c r="M26" s="1"/>
@@ -8886,11 +8798,11 @@
       <c r="AB26"/>
       <c r="AC26"/>
       <c r="AD26" s="20">
-        <v>91844</v>
+        <v>221</v>
       </c>
       <c r="AE26"/>
       <c r="AF26" s="21">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AG26" s="22">
         <v>0</v>
@@ -8942,7 +8854,7 @@
       <c r="B27" s="13"/>
       <c r="C27" s="14" t="inlineStr">
         <is>
-          <t>B0D8154CWN</t>
+          <t>B0DD49XPMY</t>
         </is>
       </c>
       <c r="D27" s="14"/>
@@ -8955,23 +8867,23 @@
       </c>
       <c r="H27" s="14" t="inlineStr">
         <is>
-          <t>Vax SpinScrub Power Upright Carpet &amp; Upholstery Cleaner Machine CDCW-SSXSsRug shampooer &amp; handheld spot cleaner, deep stain</t>
+          <t>Shark StainStriker HairPro Pet Spot Cleaner, Carpet &amp; Upholstory CleanersAnti-Clog Pet Hair Extractor, Removes Tough Stains</t>
         </is>
       </c>
       <c r="I27" s="14"/>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0D8154CWN?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/7149mbLCp1L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>B0D8154CWN</t>
+          <t>B0DD49XPMY</t>
         </is>
       </c>
       <c r="M27" s="1"/>
@@ -8992,11 +8904,11 @@
       <c r="AB27"/>
       <c r="AC27"/>
       <c r="AD27" s="20">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="AE27"/>
       <c r="AF27" s="21">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AG27" s="22">
         <v>0</v>
@@ -9048,7 +8960,7 @@
       <c r="B28" s="13"/>
       <c r="C28" s="14" t="inlineStr">
         <is>
-          <t>B0DD49XPMY</t>
+          <t>B0DD4CNLP5</t>
         </is>
       </c>
       <c r="D28" s="14"/>
@@ -9061,23 +8973,23 @@
       </c>
       <c r="H28" s="14" t="inlineStr">
         <is>
-          <t>Shark StainStriker HairPro Pet Spot Cleaner, Carpet &amp; Upholstory CleanersAnti-Clog Pet Hair Extractor, Removes Tough Stains</t>
+          <t>Shark CarpetXpert HairPro Pet Carpet Cleaner, Anti-Tangle &amp; Clog, EX300UKsBuilt-In StainStriker Spot Cleaner, Removes Tough</t>
         </is>
       </c>
       <c r="I28" s="14"/>
       <c r="J28" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DD4CNLP5?psc=1</t>
         </is>
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+fLfuSP8L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
         <is>
-          <t>B0DD49XPMY</t>
+          <t>B0DD4CNLP5</t>
         </is>
       </c>
       <c r="M28" s="1"/>
@@ -9098,11 +9010,11 @@
       <c r="AB28"/>
       <c r="AC28"/>
       <c r="AD28" s="20">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="AE28"/>
       <c r="AF28" s="21">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AG28" s="22">
         <v>0</v>
@@ -9154,7 +9066,7 @@
       <c r="B29" s="13"/>
       <c r="C29" s="14" t="inlineStr">
         <is>
-          <t>B0DD4CNLP5</t>
+          <t>B0DDKXF7NQ</t>
         </is>
       </c>
       <c r="D29" s="14"/>
@@ -9167,23 +9079,23 @@
       </c>
       <c r="H29" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetXpert HairPro Pet Carpet Cleaner, Anti-Tangle &amp; Clog, EX300UKsBuilt-In StainStriker Spot Cleaner, Removes Tough</t>
+          <t>Rivenara Carpet Spot Upholstery Cleaner - Handheld Sofa Stain Striker 450W Wet Washer Machines Vacuum Portable Compact Cleani</t>
         </is>
       </c>
       <c r="I29" s="14"/>
       <c r="J29" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DD4CNLP5?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DDKXF7NQ?psc=1</t>
         </is>
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+fLfuSP8L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
         <is>
-          <t>B0DD4CNLP5</t>
+          <t>B0DDKXF7NQ</t>
         </is>
       </c>
       <c r="M29" s="1"/>
@@ -9204,11 +9116,11 @@
       <c r="AB29"/>
       <c r="AC29"/>
       <c r="AD29" s="20">
-        <v>221</v>
+        <v>959</v>
       </c>
       <c r="AE29"/>
       <c r="AF29" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG29" s="22">
         <v>0</v>
@@ -9260,7 +9172,7 @@
       <c r="B30" s="13"/>
       <c r="C30" s="14" t="inlineStr">
         <is>
-          <t>B0DDKXF7NQ</t>
+          <t>B0DNJZP6D7</t>
         </is>
       </c>
       <c r="D30" s="14"/>
@@ -9273,23 +9185,23 @@
       </c>
       <c r="H30" s="14" t="inlineStr">
         <is>
-          <t>Rivenara Carpet Spot Upholstery Cleaner - Handheld Sofa Stain Striker 450W Wet Washer Machines Vacuum Portable Compact Cleani</t>
+          <t>Kärcher SE 3 Compact Spot Cleaner, power: 500 W, fresh water tank: 1.7 l, area: 2.76 m2, weight: 4.1 kg, spray suction hose,</t>
         </is>
       </c>
       <c r="I30" s="14"/>
       <c r="J30" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DDKXF7NQ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DNJZP6D7?psc=1</t>
         </is>
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/81NJNt2il4L._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
         <is>
-          <t>B0DDKXF7NQ</t>
+          <t>B0DNJZP6D7</t>
         </is>
       </c>
       <c r="M30" s="1"/>
@@ -9310,11 +9222,11 @@
       <c r="AB30"/>
       <c r="AC30"/>
       <c r="AD30" s="20">
-        <v>959</v>
+        <v>82</v>
       </c>
       <c r="AE30"/>
       <c r="AF30" s="21">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AG30" s="22">
         <v>0</v>
@@ -9366,7 +9278,7 @@
       <c r="B31" s="13"/>
       <c r="C31" s="14" t="inlineStr">
         <is>
-          <t>B0DNJZP6D7</t>
+          <t>B0DPGJ7V4J</t>
         </is>
       </c>
       <c r="D31" s="14"/>
@@ -9379,23 +9291,23 @@
       </c>
       <c r="H31" s="14" t="inlineStr">
         <is>
-          <t>Kärcher SE 3 Compact Spot Cleaner, power: 500 W, fresh water tank: 1.7 l, area: 2.76 m2, weight: 4.1 kg, spray suction hose,</t>
+          <t>BISSELL SpotClean C5 Pet Portable Spot Cleaner 3928EsCompact upholstery cleaner with Two-Tank Technology and a 1.7m hose, r</t>
         </is>
       </c>
       <c r="I31" s="14"/>
       <c r="J31" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DNJZP6D7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DPGJ7V4J?psc=1</t>
         </is>
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/81NJNt2il4L._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61VNJPatPVL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
         <is>
-          <t>B0DNJZP6D7</t>
+          <t>B0DPGJ7V4J</t>
         </is>
       </c>
       <c r="M31" s="1"/>
@@ -9416,11 +9328,11 @@
       <c r="AB31"/>
       <c r="AC31"/>
       <c r="AD31" s="20">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="AE31"/>
       <c r="AF31" s="21">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="AG31" s="22">
         <v>0</v>
@@ -9472,7 +9384,7 @@
       <c r="B32" s="13"/>
       <c r="C32" s="14" t="inlineStr">
         <is>
-          <t>B0DPGJ7V4J</t>
+          <t>B0DSZVCZ6P</t>
         </is>
       </c>
       <c r="D32" s="14"/>
@@ -9485,23 +9397,23 @@
       </c>
       <c r="H32" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean C5 Pet Portable Spot Cleaner 3928EsCompact upholstery cleaner with Two-Tank Technology and a 1.7m hose, r</t>
+          <t>Carpet Cleaner &amp; Spot Cleaner, Handheld Carpet Cleaner MachinessUpholstery Cleaner | Clean Up Spills &amp; Pet Messes from Carp</t>
         </is>
       </c>
       <c r="I32" s="14"/>
       <c r="J32" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DPGJ7V4J?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1</t>
         </is>
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61VNJPatPVL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
         <is>
-          <t>B0DPGJ7V4J</t>
+          <t>B0DSZVCZ6P</t>
         </is>
       </c>
       <c r="M32" s="1"/>
@@ -9522,11 +9434,11 @@
       <c r="AB32"/>
       <c r="AC32"/>
       <c r="AD32" s="20">
-        <v>61</v>
+        <v>343</v>
       </c>
       <c r="AE32"/>
       <c r="AF32" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG32" s="22">
         <v>0</v>
@@ -9578,7 +9490,7 @@
       <c r="B33" s="13"/>
       <c r="C33" s="14" t="inlineStr">
         <is>
-          <t>B0DSZVCZ6P</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="D33" s="14"/>
@@ -9591,23 +9503,23 @@
       </c>
       <c r="H33" s="14" t="inlineStr">
         <is>
-          <t>Carpet Cleaner &amp; Spot Cleaner, Handheld Carpet Cleaner MachinessUpholstery Cleaner | Clean Up Spills &amp; Pet Messes from Carp</t>
+          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
         </is>
       </c>
       <c r="I33" s="14"/>
       <c r="J33" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
         </is>
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
         <is>
-          <t>B0DSZVCZ6P</t>
+          <t>B0F2J9921T</t>
         </is>
       </c>
       <c r="M33" s="1"/>
@@ -9628,11 +9540,11 @@
       <c r="AB33"/>
       <c r="AC33"/>
       <c r="AD33" s="20">
-        <v>343</v>
+        <v>20</v>
       </c>
       <c r="AE33"/>
       <c r="AF33" s="21">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AG33" s="22">
         <v>0</v>
@@ -9684,7 +9596,7 @@
       <c r="B34" s="13"/>
       <c r="C34" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0F6CX96F9</t>
         </is>
       </c>
       <c r="D34" s="14"/>
@@ -9697,23 +9609,23 @@
       </c>
       <c r="H34" s="14" t="inlineStr">
         <is>
-          <t>Beldray Compact Spotbuster Spot Cleaner With Spray, Scrub, Vacuum, 1.3LsExtendable Hose, Scrubbing Brush Head, Dual Tank 80</t>
+          <t>BISSELL SpotClean Mini Corded Portable Carpet Cleaner 4149EsCompact and lightweight spot washer for quick cleanups, on-the-</t>
         </is>
       </c>
       <c r="I34" s="14"/>
       <c r="J34" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F2J9921T?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1</t>
         </is>
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
         <is>
-          <t>B0F2J9921T</t>
+          <t>B0F6CX96F9</t>
         </is>
       </c>
       <c r="M34" s="1"/>
@@ -9734,11 +9646,11 @@
       <c r="AB34"/>
       <c r="AC34"/>
       <c r="AD34" s="20">
-        <v>20</v>
+        <v>70</v>
       </c>
       <c r="AE34"/>
       <c r="AF34" s="21">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AG34" s="22">
         <v>0</v>
@@ -9790,7 +9702,7 @@
       <c r="B35" s="13"/>
       <c r="C35" s="14" t="inlineStr">
         <is>
-          <t>B0F6CX96F9</t>
+          <t>B0FFBK68QW</t>
         </is>
       </c>
       <c r="D35" s="14"/>
@@ -9803,23 +9715,23 @@
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>BISSELL SpotClean Mini Corded Portable Carpet Cleaner 4149EsCompact and lightweight spot washer for quick cleanups, on-the-</t>
+          <t>BISSELL PowerWash Compact Carpet Cleaner 600W 4055EsRemoves stains and odours, portable, multi-surface rug cleaner, 76 dBa,</t>
         </is>
       </c>
       <c r="I35" s="14"/>
       <c r="J35" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FFBK68QW?psc=1</t>
         </is>
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/614Fa4ryPRL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
         <is>
-          <t>B0F6CX96F9</t>
+          <t>B0FFBK68QW</t>
         </is>
       </c>
       <c r="M35" s="1"/>
@@ -9840,11 +9752,11 @@
       <c r="AB35"/>
       <c r="AC35"/>
       <c r="AD35" s="20">
-        <v>70</v>
+        <v>181</v>
       </c>
       <c r="AE35"/>
       <c r="AF35" s="21">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="AG35" s="22">
         <v>0</v>
@@ -9896,7 +9808,7 @@
       <c r="B36" s="13"/>
       <c r="C36" s="14" t="inlineStr">
         <is>
-          <t>B0FFBK68QW</t>
+          <t>B0FKGYK25M</t>
         </is>
       </c>
       <c r="D36" s="14"/>
@@ -9909,23 +9821,23 @@
       </c>
       <c r="H36" s="14" t="inlineStr">
         <is>
-          <t>BISSELL PowerWash Compact Carpet Cleaner 600W 4055EsRemoves stains and odours, portable, multi-surface rug cleaner, 76 dBa,</t>
+          <t>VickyHome Spot Cleaner, 450W Portable Carpet &amp; Upholstery Cleaner Sofa and Carpet Cleaning Machine, Lightweight Handheld Floo</t>
         </is>
       </c>
       <c r="I36" s="14"/>
       <c r="J36" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FFBK68QW?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1</t>
         </is>
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/614Fa4ryPRL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71awaqy5avL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
         <is>
-          <t>B0FFBK68QW</t>
+          <t>B0FKGYK25M</t>
         </is>
       </c>
       <c r="M36" s="1"/>
@@ -9946,11 +9858,11 @@
       <c r="AB36"/>
       <c r="AC36"/>
       <c r="AD36" s="20">
-        <v>181</v>
+        <v>28</v>
       </c>
       <c r="AE36"/>
       <c r="AF36" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG36" s="22">
         <v>0</v>
@@ -10002,7 +9914,7 @@
       <c r="B37" s="13"/>
       <c r="C37" s="14" t="inlineStr">
         <is>
-          <t>B0FKGYK25M</t>
+          <t>B0FMRPX6P7</t>
         </is>
       </c>
       <c r="D37" s="14"/>
@@ -10015,23 +9927,23 @@
       </c>
       <c r="H37" s="14" t="inlineStr">
         <is>
-          <t>VickyHome Spot Cleaner, 450W Portable Carpet &amp; Upholstery Cleaner Sofa and Carpet Cleaning Machine, Lightweight Handheld Floo</t>
+          <t>Shark StainForce Cordless Spot Cleaner, Lightweight &amp; Portable HX100UKTsSpot, Stain &amp; Odour Eliminator for Carpets, Upholst</t>
         </is>
       </c>
       <c r="I37" s="14"/>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FMRPX6P7?psc=1</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71awaqy5avL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>B0FKGYK25M</t>
+          <t>B0FMRPX6P7</t>
         </is>
       </c>
       <c r="M37" s="1"/>
@@ -10052,11 +9964,11 @@
       <c r="AB37"/>
       <c r="AC37"/>
       <c r="AD37" s="20">
-        <v>28</v>
+        <v>548</v>
       </c>
       <c r="AE37"/>
       <c r="AF37" s="21">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="AG37" s="22">
         <v>0</v>
@@ -10108,7 +10020,7 @@
       <c r="B38" s="13"/>
       <c r="C38" s="14" t="inlineStr">
         <is>
-          <t>B0FMRPX6P7</t>
+          <t>B0FP2ZHPNR</t>
         </is>
       </c>
       <c r="D38" s="14"/>
@@ -10121,23 +10033,23 @@
       </c>
       <c r="H38" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Cordless Spot Cleaner, Lightweight &amp; Portable HX100UKTsSpot, Stain &amp; Odour Eliminator for Carpets, Upholst</t>
+          <t>Kärcher SE 2 Spot Care Spot Cleaner, 1.5 l Fresh Water TanksPower consumption: 450 W, area: 2.89 m², weight: 4.2 kg, spray</t>
         </is>
       </c>
       <c r="I38" s="14"/>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FMRPX6P7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>B0FMRPX6P7</t>
+          <t>B0FP2ZHPNR</t>
         </is>
       </c>
       <c r="M38" s="1"/>
@@ -10153,16 +10065,18 @@
       <c r="W38" s="15"/>
       <c r="X38" s="15"/>
       <c r="Y38"/>
-      <c r="Z38" s="19"/>
+      <c r="Z38" s="19">
+        <v>82.5</v>
+      </c>
       <c r="AA38"/>
       <c r="AB38"/>
       <c r="AC38"/>
       <c r="AD38" s="20">
-        <v>548</v>
+        <v>95</v>
       </c>
       <c r="AE38"/>
       <c r="AF38" s="21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AG38" s="22">
         <v>0</v>
@@ -10214,7 +10128,7 @@
       <c r="B39" s="13"/>
       <c r="C39" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B0FZBSDZ26</t>
         </is>
       </c>
       <c r="D39" s="14"/>
@@ -10227,23 +10141,23 @@
       </c>
       <c r="H39" s="14" t="inlineStr">
         <is>
-          <t>Shark StainForce Dual-Formula Refill Cartridge, 2 x 500ml XSKBDHXCM500UKsValue 2-Pack, Formulated to tackle tough stains an</t>
+          <t>Vonhaus Spot Cleaner 600W Handheld Carpet Cleaner with Crevice &amp; Pet Brushs1.5L Carpet Washer &amp; Sofa Cleaner Machine with S</t>
         </is>
       </c>
       <c r="I39" s="14"/>
       <c r="J39" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1</t>
         </is>
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
         <is>
-          <t>B0FNX6YLCJ</t>
+          <t>B0FZBSDZ26</t>
         </is>
       </c>
       <c r="M39" s="1"/>
@@ -10264,11 +10178,11 @@
       <c r="AB39"/>
       <c r="AC39"/>
       <c r="AD39" s="20">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="AE39"/>
       <c r="AF39" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG39" s="22">
         <v>0</v>
@@ -10320,7 +10234,7 @@
       <c r="B40" s="13"/>
       <c r="C40" s="14" t="inlineStr">
         <is>
-          <t>B0FP2ZHPNR</t>
+          <t>B0GCZXR7BP</t>
         </is>
       </c>
       <c r="D40" s="14"/>
@@ -10333,23 +10247,23 @@
       </c>
       <c r="H40" s="14" t="inlineStr">
         <is>
-          <t>Kärcher SE 2 Spot Care Spot Cleaner, 1.5 l Fresh Water TanksPower consumption: 450 W, area: 2.89 m², weight: 4.2 kg, spray</t>
+          <t>Uwant Y100 Steam Carpet Cleaner Machine, 1750W 18kPa, 7-in-1 Multi-ToolssSelf-Cleaning Hose, for Multi-Surface Spills/Pet M</t>
         </is>
       </c>
       <c r="I40" s="14"/>
       <c r="J40" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1</t>
         </is>
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
         <is>
-          <t>B0FP2ZHPNR</t>
+          <t>B0GCZXR7BP</t>
         </is>
       </c>
       <c r="M40" s="1"/>
@@ -10365,18 +10279,16 @@
       <c r="W40" s="15"/>
       <c r="X40" s="15"/>
       <c r="Y40"/>
-      <c r="Z40" s="19">
-        <v>82.5</v>
-      </c>
+      <c r="Z40" s="19"/>
       <c r="AA40"/>
       <c r="AB40"/>
       <c r="AC40"/>
       <c r="AD40" s="20">
-        <v>95</v>
+        <v>78</v>
       </c>
       <c r="AE40"/>
       <c r="AF40" s="21">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AG40" s="22">
         <v>0</v>
@@ -10428,7 +10340,7 @@
       <c r="B41" s="13"/>
       <c r="C41" s="14" t="inlineStr">
         <is>
-          <t>B0FZBSDZ26</t>
+          <t>B0GDX2S5H7</t>
         </is>
       </c>
       <c r="D41" s="14"/>
@@ -10441,23 +10353,23 @@
       </c>
       <c r="H41" s="14" t="inlineStr">
         <is>
-          <t>Vonhaus Spot Cleaner 600W Handheld Carpet Cleaner with Crevice &amp; Pet Brushs1.5L Carpet Washer &amp; Sofa Cleaner Machine with S</t>
+          <t>Akitas X5 Spot Cleaner, 2.5kg Lightweight Handheld Design,Fabric Cleaning Solution – Trial Size, Dual Water Tanks, Ideal for</t>
         </is>
       </c>
       <c r="I41" s="14"/>
       <c r="J41" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GDX2S5H7?psc=1</t>
         </is>
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71Z+ftvAJGL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>B0FZBSDZ26</t>
+          <t>B0GDX2S5H7</t>
         </is>
       </c>
       <c r="M41" s="1"/>
@@ -10478,11 +10390,11 @@
       <c r="AB41"/>
       <c r="AC41"/>
       <c r="AD41" s="20">
-        <v>64</v>
+        <v>728</v>
       </c>
       <c r="AE41"/>
       <c r="AF41" s="21">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AG41" s="22">
         <v>0</v>
@@ -10534,7 +10446,7 @@
       <c r="B42" s="13"/>
       <c r="C42" s="14" t="inlineStr">
         <is>
-          <t>B0GCZXR7BP</t>
+          <t>B0GGB1CT2G</t>
         </is>
       </c>
       <c r="D42" s="14"/>
@@ -10547,23 +10459,23 @@
       </c>
       <c r="H42" s="14" t="inlineStr">
         <is>
-          <t>Uwant Y100 Steam Carpet Cleaner Machine, 1750W 18kPa, 7-in-1 Multi-ToolssSelf-Cleaning Hose, for Multi-Surface Spills/Pet M</t>
+          <t>Olvy Carpet Cleaner Upholstery Spot Washer Deep Stain Removals10 Piece Kit | Pro 1650W Steam | Sofa &amp; Auto Valeting | 100°C</t>
         </is>
       </c>
       <c r="I42" s="14"/>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>B0GCZXR7BP</t>
+          <t>B0GGB1CT2G</t>
         </is>
       </c>
       <c r="M42" s="1"/>
@@ -10584,11 +10496,11 @@
       <c r="AB42"/>
       <c r="AC42"/>
       <c r="AD42" s="20">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="AE42"/>
       <c r="AF42" s="21">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG42" s="22">
         <v>0</v>
@@ -10640,7 +10552,7 @@
       <c r="B43" s="13"/>
       <c r="C43" s="14" t="inlineStr">
         <is>
-          <t>B0GDX2S5H7</t>
+          <t>B0GGB43PMN</t>
         </is>
       </c>
       <c r="D43" s="14"/>
@@ -10653,23 +10565,23 @@
       </c>
       <c r="H43" s="14" t="inlineStr">
         <is>
-          <t>Akitas X5 Spot Cleaner, 2.5kg Lightweight Handheld Design,Fabric Cleaning Solution – Trial Size, Dual Water Tanks, Ideal for</t>
+          <t>Akitas X7 600W Spot Cleaner with Starter Cleaning SolutionsCarpet &amp; Upholstery Cleaner, Self-Cleaning, Ideal for Pet Stains</t>
         </is>
       </c>
       <c r="I43" s="14"/>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GDX2S5H7?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GGB43PMN?psc=1</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71Z+ftvAJGL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71pCAazCoBL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>B0GDX2S5H7</t>
+          <t>B0GGB43PMN</t>
         </is>
       </c>
       <c r="M43" s="1"/>
@@ -10690,7 +10602,7 @@
       <c r="AB43"/>
       <c r="AC43"/>
       <c r="AD43" s="20">
-        <v>728</v>
+        <v>2385</v>
       </c>
       <c r="AE43"/>
       <c r="AF43" s="21">
@@ -10746,7 +10658,7 @@
       <c r="B44" s="13"/>
       <c r="C44" s="14" t="inlineStr">
         <is>
-          <t>B0GGB1CT2G</t>
+          <t>B0GGJB2H1M</t>
         </is>
       </c>
       <c r="D44" s="14"/>
@@ -10759,23 +10671,23 @@
       </c>
       <c r="H44" s="14" t="inlineStr">
         <is>
-          <t>Olvy Carpet Cleaner Upholstery Spot Washer Deep Stain Removals10 Piece Kit | Pro 1650W Steam | Sofa &amp; Auto Valeting | 100°C</t>
+          <t>Olsen &amp; Smith 1600W Dual-Tank Carpet &amp; Upholstrey Spot Cleaner, HandheldsCold, Warm &amp; Steam Stain Removal, Upholstery Clean</t>
         </is>
       </c>
       <c r="I44" s="14"/>
       <c r="J44" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1</t>
         </is>
       </c>
       <c r="K44" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L44" s="14" t="inlineStr">
         <is>
-          <t>B0GGB1CT2G</t>
+          <t>B0GGJB2H1M</t>
         </is>
       </c>
       <c r="M44" s="1"/>
@@ -10796,11 +10708,11 @@
       <c r="AB44"/>
       <c r="AC44"/>
       <c r="AD44" s="20">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="AE44"/>
       <c r="AF44" s="21">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="AG44" s="22">
         <v>0</v>
@@ -10852,7 +10764,7 @@
       <c r="B45" s="13"/>
       <c r="C45" s="14" t="inlineStr">
         <is>
-          <t>B0GGB43PMN</t>
+          <t>B0GQYM3S7R</t>
         </is>
       </c>
       <c r="D45" s="14"/>
@@ -10865,23 +10777,23 @@
       </c>
       <c r="H45" s="14" t="inlineStr">
         <is>
-          <t>Akitas X7 600W Spot Cleaner with Starter Cleaning SolutionsCarpet &amp; Upholstery Cleaner, Self-Cleaning, Ideal for Pet Stains</t>
+          <t>Vortisys Handheld Carpet Cleaner, Portable Spot‑Cleaner, Blue‑Blacks530W/18kPa, 2.8L Dual‑Tank Design, for Rug, Pet Messes,</t>
         </is>
       </c>
       <c r="I45" s="14"/>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GGB43PMN?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0GQYM3S7R?psc=1</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71pCAazCoBL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71ahSAftNjL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>B0GGB43PMN</t>
+          <t>B0GQYM3S7R</t>
         </is>
       </c>
       <c r="M45" s="1"/>
@@ -10902,11 +10814,11 @@
       <c r="AB45"/>
       <c r="AC45"/>
       <c r="AD45" s="20">
-        <v>2385</v>
+        <v>13</v>
       </c>
       <c r="AE45"/>
       <c r="AF45" s="21">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="AG45" s="22">
         <v>0</v>
@@ -10958,7 +10870,7 @@
       <c r="B46" s="13"/>
       <c r="C46" s="14" t="inlineStr">
         <is>
-          <t>B0GGJB2H1M</t>
+          <t>B0H1JBNL77</t>
         </is>
       </c>
       <c r="D46" s="14"/>
@@ -10971,23 +10883,23 @@
       </c>
       <c r="H46" s="14" t="inlineStr">
         <is>
-          <t>Olsen &amp; Smith 1600W Dual-Tank Carpet &amp; Upholstrey Spot Cleaner, HandheldsCold, Warm &amp; Steam Stain Removal, Upholstery Clean</t>
+          <t>Vax SpotWash Mini Duo Compact Handheld Spot Cleaner CDSW-MCXTsPortable upholstery &amp; carpet cleaner, multi-surface deep clea</t>
         </is>
       </c>
       <c r="I46" s="14"/>
       <c r="J46" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H1JBNL77?psc=1</t>
         </is>
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/71cBtcb4DrL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
         <is>
-          <t>B0GGJB2H1M</t>
+          <t>B0H1JBNL77</t>
         </is>
       </c>
       <c r="M46" s="1"/>
@@ -11003,16 +10915,18 @@
       <c r="W46" s="15"/>
       <c r="X46" s="15"/>
       <c r="Y46"/>
-      <c r="Z46" s="19"/>
+      <c r="Z46" s="19">
+        <v>91.52</v>
+      </c>
       <c r="AA46"/>
       <c r="AB46"/>
       <c r="AC46"/>
       <c r="AD46" s="20">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="AE46"/>
       <c r="AF46" s="21">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG46" s="22">
         <v>0</v>
@@ -11064,7 +10978,7 @@
       <c r="B47" s="13"/>
       <c r="C47" s="14" t="inlineStr">
         <is>
-          <t>B0GQYM3S7R</t>
+          <t>B0H6KDXVQ5</t>
         </is>
       </c>
       <c r="D47" s="14"/>
@@ -11077,23 +10991,23 @@
       </c>
       <c r="H47" s="14" t="inlineStr">
         <is>
-          <t>Vortisys Handheld Carpet Cleaner, Portable Spot‑Cleaner, Blue‑Blacks530W/18kPa, 2.8L Dual‑Tank Design, for Rug, Pet Messes,</t>
+          <t>Shark CarpetForce Ultra Upright Carpet Cleaner with HairPro, EX550UKCPs2 Bottles of Deep Clean Ultra Solution, PowerFins Br</t>
         </is>
       </c>
       <c r="I47" s="14"/>
       <c r="J47" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0GQYM3S7R?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1</t>
         </is>
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71ahSAftNjL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61WO-PNCGuL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
         <is>
-          <t>B0GQYM3S7R</t>
+          <t>B0H6KDXVQ5</t>
         </is>
       </c>
       <c r="M47" s="1"/>
@@ -11114,11 +11028,11 @@
       <c r="AB47"/>
       <c r="AC47"/>
       <c r="AD47" s="20">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="AE47"/>
       <c r="AF47" s="21">
-        <v>4.1</v>
+        <v>4.7</v>
       </c>
       <c r="AG47" s="22">
         <v>0</v>
@@ -11170,7 +11084,7 @@
       <c r="B48" s="13"/>
       <c r="C48" s="14" t="inlineStr">
         <is>
-          <t>B0H1JBNL77</t>
+          <t>B0H98GCFZB</t>
         </is>
       </c>
       <c r="D48" s="14"/>
@@ -11183,23 +11097,23 @@
       </c>
       <c r="H48" s="14" t="inlineStr">
         <is>
-          <t>Vax SpotWash Mini Duo Compact Handheld Spot Cleaner CDSW-MCXTsPortable upholstery &amp; carpet cleaner, multi-surface deep clea</t>
+          <t>STARRYBOT Steam Carpet and Upholstery Cleaner, 1500W, 22KPasSteam cleaner tackles stains on rugs, stairs, sofas and car sea</t>
         </is>
       </c>
       <c r="I48" s="14"/>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H1JBNL77?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/71cBtcb4DrL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>B0H1JBNL77</t>
+          <t>B0H98GCFZB</t>
         </is>
       </c>
       <c r="M48" s="1"/>
@@ -11215,18 +11129,16 @@
       <c r="W48" s="15"/>
       <c r="X48" s="15"/>
       <c r="Y48"/>
-      <c r="Z48" s="19">
-        <v>91.52</v>
-      </c>
+      <c r="Z48" s="19"/>
       <c r="AA48"/>
       <c r="AB48"/>
       <c r="AC48"/>
       <c r="AD48" s="20">
-        <v>92</v>
+        <v>55</v>
       </c>
       <c r="AE48"/>
       <c r="AF48" s="21">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="AG48" s="22">
         <v>0</v>
@@ -11278,7 +11190,7 @@
       <c r="B49" s="13"/>
       <c r="C49" s="14" t="inlineStr">
         <is>
-          <t>B0H6KDXVQ5</t>
+          <t>B0HC816GR1</t>
         </is>
       </c>
       <c r="D49" s="14"/>
@@ -11291,23 +11203,23 @@
       </c>
       <c r="H49" s="14" t="inlineStr">
         <is>
-          <t>Shark CarpetForce Ultra Upright Carpet Cleaner with HairPro, EX550UKCPs2 Bottles of Deep Clean Ultra Solution, PowerFins Br</t>
+          <t>Vax MAXClean StainShot Pet Upholstery &amp; Carpet Cleaner Machine, CDCW-MCAPsPowerful upright shampooer for pet stains, sofas</t>
         </is>
       </c>
       <c r="I49" s="14"/>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1</t>
+          <t>https://www.amazon.co.uk/dp/B0HC816GR1?psc=1</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61WO-PNCGuL._AC_UL300_SR300,200_.jpg</t>
+          <t>https://images-eu.ssl-images-amazon.com/images/I/717QutrBkcL._AC_UL300_SR300,200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>B0H6KDXVQ5</t>
+          <t>B0HC816GR1</t>
         </is>
       </c>
       <c r="M49" s="1"/>
@@ -11327,13 +11239,9 @@
       <c r="AA49"/>
       <c r="AB49"/>
       <c r="AC49"/>
-      <c r="AD49" s="20">
-        <v>28</v>
-      </c>
+      <c r="AD49" s="20"/>
       <c r="AE49"/>
-      <c r="AF49" s="21">
-        <v>4.7</v>
-      </c>
+      <c r="AF49" s="21"/>
       <c r="AG49" s="22">
         <v>0</v>
       </c>
@@ -11376,214 +11284,6 @@
       <c r="BP49"/>
       <c r="BQ49" s="23"/>
       <c r="BR49"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="13">
-        <v>49</v>
-      </c>
-      <c r="B50" s="13"/>
-      <c r="C50" s="14" t="inlineStr">
-        <is>
-          <t>B0H98GCFZB</t>
-        </is>
-      </c>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50"/>
-      <c r="G50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H50" s="14" t="inlineStr">
-        <is>
-          <t>STARRYBOT Steam Carpet and Upholstery Cleaner, 1500W, 22KPasSteam cleaner tackles stains on rugs, stairs, sofas and car sea</t>
-        </is>
-      </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="14" t="inlineStr">
-        <is>
-          <t>B0H98GCFZB</t>
-        </is>
-      </c>
-      <c r="M50" s="1"/>
-      <c r="N50" s="14"/>
-      <c r="O50" s="15"/>
-      <c r="P50" s="15"/>
-      <c r="Q50" s="16"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="18"/>
-      <c r="T50" s="15"/>
-      <c r="U50" s="16"/>
-      <c r="V50" s="15"/>
-      <c r="W50" s="15"/>
-      <c r="X50" s="15"/>
-      <c r="Y50"/>
-      <c r="Z50" s="19"/>
-      <c r="AA50"/>
-      <c r="AB50"/>
-      <c r="AC50"/>
-      <c r="AD50" s="20">
-        <v>55</v>
-      </c>
-      <c r="AE50"/>
-      <c r="AF50" s="21">
-        <v>5</v>
-      </c>
-      <c r="AG50" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH50"/>
-      <c r="AI50" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="1"/>
-      <c r="AL50" s="20"/>
-      <c r="AM50"/>
-      <c r="AN50" s="13"/>
-      <c r="AO50" s="13"/>
-      <c r="AP50"/>
-      <c r="AQ50" s="20"/>
-      <c r="AR50"/>
-      <c r="AS50"/>
-      <c r="AT50"/>
-      <c r="AU50" s="13"/>
-      <c r="AV50" s="14"/>
-      <c r="AW50" s="13"/>
-      <c r="AX50" s="13"/>
-      <c r="AY50" s="13"/>
-      <c r="AZ50" s="13"/>
-      <c r="BA50" s="13"/>
-      <c r="BB50" s="13"/>
-      <c r="BC50" s="13"/>
-      <c r="BD50" s="13"/>
-      <c r="BE50" s="13"/>
-      <c r="BF50" s="13"/>
-      <c r="BG50" s="13"/>
-      <c r="BH50" s="14"/>
-      <c r="BI50"/>
-      <c r="BJ50"/>
-      <c r="BK50" s="23"/>
-      <c r="BL50"/>
-      <c r="BM50" s="23"/>
-      <c r="BN50"/>
-      <c r="BO50" s="23"/>
-      <c r="BP50"/>
-      <c r="BQ50" s="23"/>
-      <c r="BR50"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="13">
-        <v>50</v>
-      </c>
-      <c r="B51" s="13"/>
-      <c r="C51" s="14" t="inlineStr">
-        <is>
-          <t>B0HC816GR1</t>
-        </is>
-      </c>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51"/>
-      <c r="G51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.ukundefined</t>
-        </is>
-      </c>
-      <c r="H51" s="14" t="inlineStr">
-        <is>
-          <t>Vax MAXClean StainShot Pet Upholstery &amp; Carpet Cleaner Machine, CDCW-MCAPsPowerful upright shampooer for pet stains, sofas</t>
-        </is>
-      </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.uk/dp/B0HC816GR1?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="14" t="inlineStr">
-        <is>
-          <t>https://images-eu.ssl-images-amazon.com/images/I/717QutrBkcL._AC_UL300_SR300,200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="14" t="inlineStr">
-        <is>
-          <t>B0HC816GR1</t>
-        </is>
-      </c>
-      <c r="M51" s="1"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="15"/>
-      <c r="P51" s="15"/>
-      <c r="Q51" s="16"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="18"/>
-      <c r="T51" s="15"/>
-      <c r="U51" s="16"/>
-      <c r="V51" s="15"/>
-      <c r="W51" s="15"/>
-      <c r="X51" s="15"/>
-      <c r="Y51"/>
-      <c r="Z51" s="19"/>
-      <c r="AA51"/>
-      <c r="AB51"/>
-      <c r="AC51"/>
-      <c r="AD51" s="20"/>
-      <c r="AE51"/>
-      <c r="AF51" s="21"/>
-      <c r="AG51" s="22">
-        <v>0</v>
-      </c>
-      <c r="AH51"/>
-      <c r="AI51" s="16">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="1"/>
-      <c r="AL51" s="20"/>
-      <c r="AM51"/>
-      <c r="AN51" s="13"/>
-      <c r="AO51" s="13"/>
-      <c r="AP51"/>
-      <c r="AQ51" s="20"/>
-      <c r="AR51"/>
-      <c r="AS51"/>
-      <c r="AT51"/>
-      <c r="AU51" s="13"/>
-      <c r="AV51" s="14"/>
-      <c r="AW51" s="13"/>
-      <c r="AX51" s="13"/>
-      <c r="AY51" s="13"/>
-      <c r="AZ51" s="13"/>
-      <c r="BA51" s="13"/>
-      <c r="BB51" s="13"/>
-      <c r="BC51" s="13"/>
-      <c r="BD51" s="13"/>
-      <c r="BE51" s="13"/>
-      <c r="BF51" s="13"/>
-      <c r="BG51" s="13"/>
-      <c r="BH51" s="14"/>
-      <c r="BI51"/>
-      <c r="BJ51"/>
-      <c r="BK51" s="23"/>
-      <c r="BL51"/>
-      <c r="BM51" s="23"/>
-      <c r="BN51"/>
-      <c r="BO51" s="23"/>
-      <c r="BP51"/>
-      <c r="BQ51" s="23"/>
-      <c r="BR51"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11629,218 +11329,208 @@
     <hyperlink ref="J9" r:id="rId38" tooltip="https://www.amazon.co.uk/dp/B072XRJTT9?psc=1"/>
     <hyperlink ref="K9" r:id="rId39" tooltip="https://images-eu.ssl-images-amazon.com/images/I/618OSTSs2kL._AC_UL300_SR300,200_.jpg"/>
     <hyperlink ref="L9" r:id="rId40" tooltip="https://www.amazon.co.uk/dp/B072XRJTT9"/>
-    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
+    <hyperlink ref="C10" r:id="rId41" tooltip="https://www.amazon.co.uk/dp/B07CH4WZJ9"/>
     <hyperlink ref="G10" r:id="rId42" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR?psc=1"/>
-    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/51-YKuNNnoL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.uk/dp/B0753NXDPR"/>
-    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B07CH4WZJ9"/>
+    <hyperlink ref="J10" r:id="rId43" tooltip="https://www.amazon.co.uk/dp/B07CH4WZJ9?psc=1"/>
+    <hyperlink ref="K10" r:id="rId44" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61cy6Zl-hUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L10" r:id="rId45" tooltip="https://www.amazon.co.uk/dp/B07CH4WZJ9"/>
+    <hyperlink ref="C11" r:id="rId46" tooltip="https://www.amazon.co.uk/dp/B07MWDYH1F"/>
     <hyperlink ref="G11" r:id="rId47" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B07CH4WZJ9?psc=1"/>
-    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61cy6Zl-hUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B07CH4WZJ9"/>
-    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B07MWDYH1F"/>
+    <hyperlink ref="J11" r:id="rId48" tooltip="https://www.amazon.co.uk/dp/B07MWDYH1F?psc=1"/>
+    <hyperlink ref="K11" r:id="rId49" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61hzbjuSlWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L11" r:id="rId50" tooltip="https://www.amazon.co.uk/dp/B07MWDYH1F"/>
+    <hyperlink ref="C12" r:id="rId51" tooltip="https://www.amazon.co.uk/dp/B08XK5C5TT"/>
     <hyperlink ref="G12" r:id="rId52" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B07MWDYH1F?psc=1"/>
-    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61hzbjuSlWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B07MWDYH1F"/>
-    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B08XK5C5TT"/>
+    <hyperlink ref="J12" r:id="rId53" tooltip="https://www.amazon.co.uk/dp/B08XK5C5TT?psc=1"/>
+    <hyperlink ref="K12" r:id="rId54" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7141egivyQL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L12" r:id="rId55" tooltip="https://www.amazon.co.uk/dp/B08XK5C5TT"/>
+    <hyperlink ref="C13" r:id="rId56" tooltip="https://www.amazon.co.uk/dp/B09RZDRFPP"/>
     <hyperlink ref="G13" r:id="rId57" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B08XK5C5TT?psc=1"/>
-    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7141egivyQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B08XK5C5TT"/>
-    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B09RZDRFPP"/>
+    <hyperlink ref="J13" r:id="rId58" tooltip="https://www.amazon.co.uk/dp/B09RZDRFPP?psc=1"/>
+    <hyperlink ref="K13" r:id="rId59" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ofQFCHaWL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L13" r:id="rId60" tooltip="https://www.amazon.co.uk/dp/B09RZDRFPP"/>
+    <hyperlink ref="C14" r:id="rId61" tooltip="https://www.amazon.co.uk/dp/B09RZPB79W"/>
     <hyperlink ref="G14" r:id="rId62" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B09RZDRFPP?psc=1"/>
-    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ofQFCHaWL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B09RZDRFPP"/>
-    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B09RZPB79W"/>
+    <hyperlink ref="J14" r:id="rId63" tooltip="https://www.amazon.co.uk/dp/B09RZPB79W?psc=1"/>
+    <hyperlink ref="K14" r:id="rId64" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TTHRPYsjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L14" r:id="rId65" tooltip="https://www.amazon.co.uk/dp/B09RZPB79W"/>
+    <hyperlink ref="C15" r:id="rId66" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
     <hyperlink ref="G15" r:id="rId67" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B09RZPB79W?psc=1"/>
-    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TTHRPYsjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B09RZPB79W"/>
-    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="J15" r:id="rId68" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
+    <hyperlink ref="K15" r:id="rId69" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L15" r:id="rId70" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
+    <hyperlink ref="C16" r:id="rId71" tooltip="https://www.amazon.co.uk/dp/B0B5713JZW"/>
     <hyperlink ref="G16" r:id="rId72" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8?psc=1"/>
-    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61I5O-KnPsL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.co.uk/dp/B0B4JST7J8"/>
-    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B0B5713JZW"/>
+    <hyperlink ref="J16" r:id="rId73" tooltip="https://www.amazon.co.uk/dp/B0B5713JZW?psc=1"/>
+    <hyperlink ref="K16" r:id="rId74" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71kt5MoDO9L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L16" r:id="rId75" tooltip="https://www.amazon.co.uk/dp/B0B5713JZW"/>
+    <hyperlink ref="C17" r:id="rId76" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS"/>
     <hyperlink ref="G17" r:id="rId77" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.co.uk/dp/B0B5713JZW?psc=1"/>
-    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71kt5MoDO9L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.co.uk/dp/B0B5713JZW"/>
-    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS"/>
+    <hyperlink ref="J17" r:id="rId78" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS?psc=1"/>
+    <hyperlink ref="K17" r:id="rId79" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81gIVoIFeGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L17" r:id="rId80" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS"/>
+    <hyperlink ref="C18" r:id="rId81" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
     <hyperlink ref="G18" r:id="rId82" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS?psc=1"/>
-    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81gIVoIFeGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.co.uk/dp/B0BX3CS1MS"/>
-    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
+    <hyperlink ref="J18" r:id="rId83" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1"/>
+    <hyperlink ref="K18" r:id="rId84" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L18" r:id="rId85" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
+    <hyperlink ref="C19" r:id="rId86" tooltip="https://www.amazon.co.uk/dp/B0CHYQ4NMS"/>
     <hyperlink ref="G19" r:id="rId87" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH?psc=1"/>
-    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719JsBbXXGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B0CFV7HZHH"/>
-    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0CHYQ4NMS"/>
+    <hyperlink ref="J19" r:id="rId88" tooltip="https://www.amazon.co.uk/dp/B0CHYQ4NMS?psc=1"/>
+    <hyperlink ref="K19" r:id="rId89" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ae2raT2BL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L19" r:id="rId90" tooltip="https://www.amazon.co.uk/dp/B0CHYQ4NMS"/>
+    <hyperlink ref="C20" r:id="rId91" tooltip="https://www.amazon.co.uk/dp/B0CND95KY4"/>
     <hyperlink ref="G20" r:id="rId92" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B0CHYQ4NMS?psc=1"/>
-    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61ae2raT2BL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B0CHYQ4NMS"/>
-    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B0CND95KY4"/>
+    <hyperlink ref="J20" r:id="rId93" tooltip="https://www.amazon.co.uk/dp/B0CND95KY4?psc=1"/>
+    <hyperlink ref="K20" r:id="rId94" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PuJ8C+JUL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L20" r:id="rId95" tooltip="https://www.amazon.co.uk/dp/B0CND95KY4"/>
+    <hyperlink ref="C21" r:id="rId96" tooltip="https://www.amazon.co.uk/dp/B0CW1QQF4F"/>
     <hyperlink ref="G21" r:id="rId97" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B0CND95KY4?psc=1"/>
-    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71PuJ8C+JUL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.uk/dp/B0CND95KY4"/>
-    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0CW1QQF4F"/>
+    <hyperlink ref="J21" r:id="rId98" tooltip="https://www.amazon.co.uk/dp/B0CW1QQF4F?psc=1"/>
+    <hyperlink ref="K21" r:id="rId99" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61W-FhLaf+L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L21" r:id="rId100" tooltip="https://www.amazon.co.uk/dp/B0CW1QQF4F"/>
+    <hyperlink ref="C22" r:id="rId101" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
     <hyperlink ref="G22" r:id="rId102" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.uk/dp/B0CW1QQF4F?psc=1"/>
-    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61W-FhLaf+L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.uk/dp/B0CW1QQF4F"/>
-    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="J22" r:id="rId103" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
+    <hyperlink ref="K22" r:id="rId104" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L22" r:id="rId105" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
+    <hyperlink ref="C23" r:id="rId106" tooltip="https://www.amazon.co.uk/dp/B0D2LLN3GT"/>
     <hyperlink ref="G23" r:id="rId107" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT?psc=1"/>
-    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/710N6Z-MMTL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0CZRYCLNT"/>
-    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.uk/dp/B0D2LLN3GT"/>
+    <hyperlink ref="J23" r:id="rId108" tooltip="https://www.amazon.co.uk/dp/B0D2LLN3GT?psc=1"/>
+    <hyperlink ref="K23" r:id="rId109" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71WxSJgdq2L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L23" r:id="rId110" tooltip="https://www.amazon.co.uk/dp/B0D2LLN3GT"/>
+    <hyperlink ref="C24" r:id="rId111" tooltip="https://www.amazon.co.uk/dp/B0D2LNZQ7Y"/>
     <hyperlink ref="G24" r:id="rId112" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.uk/dp/B0D2LLN3GT?psc=1"/>
-    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71WxSJgdq2L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.uk/dp/B0D2LLN3GT"/>
-    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.uk/dp/B0D2LNZQ7Y"/>
+    <hyperlink ref="J24" r:id="rId113" tooltip="https://www.amazon.co.uk/dp/B0D2LNZQ7Y?psc=1"/>
+    <hyperlink ref="K24" r:id="rId114" tooltip="https://images-eu.ssl-images-amazon.com/images/I/715jhnqP5mL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L24" r:id="rId115" tooltip="https://www.amazon.co.uk/dp/B0D2LNZQ7Y"/>
+    <hyperlink ref="C25" r:id="rId116" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
     <hyperlink ref="G25" r:id="rId117" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.uk/dp/B0D2LNZQ7Y?psc=1"/>
-    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/715jhnqP5mL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.uk/dp/B0D2LNZQ7Y"/>
-    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
+    <hyperlink ref="J25" r:id="rId118" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1"/>
+    <hyperlink ref="K25" r:id="rId119" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L25" r:id="rId120" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
+    <hyperlink ref="C26" r:id="rId121" tooltip="https://www.amazon.co.uk/dp/B0D8154CWN"/>
     <hyperlink ref="G26" r:id="rId122" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X?psc=1"/>
-    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61Q4vOHN60L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.uk/dp/B0D6RSDL6X"/>
-    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.uk/dp/B0D8154CWN"/>
+    <hyperlink ref="J26" r:id="rId123" tooltip="https://www.amazon.co.uk/dp/B0D8154CWN?psc=1"/>
+    <hyperlink ref="K26" r:id="rId124" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7149mbLCp1L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L26" r:id="rId125" tooltip="https://www.amazon.co.uk/dp/B0D8154CWN"/>
+    <hyperlink ref="C27" r:id="rId126" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
     <hyperlink ref="G27" r:id="rId127" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.uk/dp/B0D8154CWN?psc=1"/>
-    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/7149mbLCp1L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.uk/dp/B0D8154CWN"/>
-    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
+    <hyperlink ref="J27" r:id="rId128" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1"/>
+    <hyperlink ref="K27" r:id="rId129" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L27" r:id="rId130" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
+    <hyperlink ref="C28" r:id="rId131" tooltip="https://www.amazon.co.uk/dp/B0DD4CNLP5"/>
     <hyperlink ref="G28" r:id="rId132" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY?psc=1"/>
-    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81+uS+NRpuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.uk/dp/B0DD49XPMY"/>
-    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.uk/dp/B0DD4CNLP5"/>
+    <hyperlink ref="J28" r:id="rId133" tooltip="https://www.amazon.co.uk/dp/B0DD4CNLP5?psc=1"/>
+    <hyperlink ref="K28" r:id="rId134" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+fLfuSP8L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L28" r:id="rId135" tooltip="https://www.amazon.co.uk/dp/B0DD4CNLP5"/>
+    <hyperlink ref="C29" r:id="rId136" tooltip="https://www.amazon.co.uk/dp/B0DDKXF7NQ"/>
     <hyperlink ref="G29" r:id="rId137" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.uk/dp/B0DD4CNLP5?psc=1"/>
-    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+fLfuSP8L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.uk/dp/B0DD4CNLP5"/>
-    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.uk/dp/B0DDKXF7NQ"/>
+    <hyperlink ref="J29" r:id="rId138" tooltip="https://www.amazon.co.uk/dp/B0DDKXF7NQ?psc=1"/>
+    <hyperlink ref="K29" r:id="rId139" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L29" r:id="rId140" tooltip="https://www.amazon.co.uk/dp/B0DDKXF7NQ"/>
+    <hyperlink ref="C30" r:id="rId141" tooltip="https://www.amazon.co.uk/dp/B0DNJZP6D7"/>
     <hyperlink ref="G30" r:id="rId142" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.uk/dp/B0DDKXF7NQ?psc=1"/>
-    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71TGCJz8hSL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.uk/dp/B0DDKXF7NQ"/>
-    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.uk/dp/B0DNJZP6D7"/>
+    <hyperlink ref="J30" r:id="rId143" tooltip="https://www.amazon.co.uk/dp/B0DNJZP6D7?psc=1"/>
+    <hyperlink ref="K30" r:id="rId144" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81NJNt2il4L._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L30" r:id="rId145" tooltip="https://www.amazon.co.uk/dp/B0DNJZP6D7"/>
+    <hyperlink ref="C31" r:id="rId146" tooltip="https://www.amazon.co.uk/dp/B0DPGJ7V4J"/>
     <hyperlink ref="G31" r:id="rId147" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.uk/dp/B0DNJZP6D7?psc=1"/>
-    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/81NJNt2il4L._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.uk/dp/B0DNJZP6D7"/>
-    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.uk/dp/B0DPGJ7V4J"/>
+    <hyperlink ref="J31" r:id="rId148" tooltip="https://www.amazon.co.uk/dp/B0DPGJ7V4J?psc=1"/>
+    <hyperlink ref="K31" r:id="rId149" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61VNJPatPVL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L31" r:id="rId150" tooltip="https://www.amazon.co.uk/dp/B0DPGJ7V4J"/>
+    <hyperlink ref="C32" r:id="rId151" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
     <hyperlink ref="G32" r:id="rId152" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.uk/dp/B0DPGJ7V4J?psc=1"/>
-    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61VNJPatPVL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.uk/dp/B0DPGJ7V4J"/>
-    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
+    <hyperlink ref="J32" r:id="rId153" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1"/>
+    <hyperlink ref="K32" r:id="rId154" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L32" r:id="rId155" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
+    <hyperlink ref="C33" r:id="rId156" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
     <hyperlink ref="G33" r:id="rId157" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P?psc=1"/>
-    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71zd5E5cORL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.uk/dp/B0DSZVCZ6P"/>
-    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="J33" r:id="rId158" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
+    <hyperlink ref="K33" r:id="rId159" tooltip="https://images-eu.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L33" r:id="rId160" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
+    <hyperlink ref="C34" r:id="rId161" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
     <hyperlink ref="G34" r:id="rId162" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T?psc=1"/>
-    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/712N3aaiNFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.uk/dp/B0F2J9921T"/>
-    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
+    <hyperlink ref="J34" r:id="rId163" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1"/>
+    <hyperlink ref="K34" r:id="rId164" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L34" r:id="rId165" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
+    <hyperlink ref="C35" r:id="rId166" tooltip="https://www.amazon.co.uk/dp/B0FFBK68QW"/>
     <hyperlink ref="G35" r:id="rId167" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9?psc=1"/>
-    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61SfSFyuxFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.uk/dp/B0F6CX96F9"/>
-    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.uk/dp/B0FFBK68QW"/>
+    <hyperlink ref="J35" r:id="rId168" tooltip="https://www.amazon.co.uk/dp/B0FFBK68QW?psc=1"/>
+    <hyperlink ref="K35" r:id="rId169" tooltip="https://images-eu.ssl-images-amazon.com/images/I/614Fa4ryPRL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L35" r:id="rId170" tooltip="https://www.amazon.co.uk/dp/B0FFBK68QW"/>
+    <hyperlink ref="C36" r:id="rId171" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
     <hyperlink ref="G36" r:id="rId172" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.uk/dp/B0FFBK68QW?psc=1"/>
-    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/614Fa4ryPRL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.uk/dp/B0FFBK68QW"/>
-    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
+    <hyperlink ref="J36" r:id="rId173" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1"/>
+    <hyperlink ref="K36" r:id="rId174" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71awaqy5avL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L36" r:id="rId175" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
+    <hyperlink ref="C37" r:id="rId176" tooltip="https://www.amazon.co.uk/dp/B0FMRPX6P7"/>
     <hyperlink ref="G37" r:id="rId177" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M?psc=1"/>
-    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71awaqy5avL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.uk/dp/B0FKGYK25M"/>
-    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.uk/dp/B0FMRPX6P7"/>
+    <hyperlink ref="J37" r:id="rId178" tooltip="https://www.amazon.co.uk/dp/B0FMRPX6P7?psc=1"/>
+    <hyperlink ref="K37" r:id="rId179" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L37" r:id="rId180" tooltip="https://www.amazon.co.uk/dp/B0FMRPX6P7"/>
+    <hyperlink ref="C38" r:id="rId181" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
     <hyperlink ref="G38" r:id="rId182" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.uk/dp/B0FMRPX6P7?psc=1"/>
-    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71H8QQLQWvL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.uk/dp/B0FMRPX6P7"/>
-    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
+    <hyperlink ref="J38" r:id="rId183" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1"/>
+    <hyperlink ref="K38" r:id="rId184" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L38" r:id="rId185" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
+    <hyperlink ref="C39" r:id="rId186" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
     <hyperlink ref="G39" r:id="rId187" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ?psc=1"/>
-    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71SuXoGPIQL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.uk/dp/B0FNX6YLCJ"/>
-    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
+    <hyperlink ref="J39" r:id="rId188" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1"/>
+    <hyperlink ref="K39" r:id="rId189" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L39" r:id="rId190" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
+    <hyperlink ref="C40" r:id="rId191" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
     <hyperlink ref="G40" r:id="rId192" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR?psc=1"/>
-    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71+CEIEPwFL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.uk/dp/B0FP2ZHPNR"/>
-    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
+    <hyperlink ref="J40" r:id="rId193" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1"/>
+    <hyperlink ref="K40" r:id="rId194" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L40" r:id="rId195" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
+    <hyperlink ref="C41" r:id="rId196" tooltip="https://www.amazon.co.uk/dp/B0GDX2S5H7"/>
     <hyperlink ref="G41" r:id="rId197" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26?psc=1"/>
-    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Dl6k2D2FL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0FZBSDZ26"/>
-    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
+    <hyperlink ref="J41" r:id="rId198" tooltip="https://www.amazon.co.uk/dp/B0GDX2S5H7?psc=1"/>
+    <hyperlink ref="K41" r:id="rId199" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Z+ftvAJGL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L41" r:id="rId200" tooltip="https://www.amazon.co.uk/dp/B0GDX2S5H7"/>
+    <hyperlink ref="C42" r:id="rId201" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
     <hyperlink ref="G42" r:id="rId202" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP?psc=1"/>
-    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71rICLqsRHL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.uk/dp/B0GCZXR7BP"/>
-    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0GDX2S5H7"/>
+    <hyperlink ref="J42" r:id="rId203" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1"/>
+    <hyperlink ref="K42" r:id="rId204" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L42" r:id="rId205" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
+    <hyperlink ref="C43" r:id="rId206" tooltip="https://www.amazon.co.uk/dp/B0GGB43PMN"/>
     <hyperlink ref="G43" r:id="rId207" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0GDX2S5H7?psc=1"/>
-    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71Z+ftvAJGL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.uk/dp/B0GDX2S5H7"/>
-    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
+    <hyperlink ref="J43" r:id="rId208" tooltip="https://www.amazon.co.uk/dp/B0GGB43PMN?psc=1"/>
+    <hyperlink ref="K43" r:id="rId209" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pCAazCoBL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L43" r:id="rId210" tooltip="https://www.amazon.co.uk/dp/B0GGB43PMN"/>
+    <hyperlink ref="C44" r:id="rId211" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
     <hyperlink ref="G44" r:id="rId212" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G?psc=1"/>
-    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71sjHKYkrdL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0GGB1CT2G"/>
-    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.uk/dp/B0GGB43PMN"/>
+    <hyperlink ref="J44" r:id="rId213" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1"/>
+    <hyperlink ref="K44" r:id="rId214" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L44" r:id="rId215" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
+    <hyperlink ref="C45" r:id="rId216" tooltip="https://www.amazon.co.uk/dp/B0GQYM3S7R"/>
     <hyperlink ref="G45" r:id="rId217" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.uk/dp/B0GGB43PMN?psc=1"/>
-    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71pCAazCoBL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0GGB43PMN"/>
-    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
+    <hyperlink ref="J45" r:id="rId218" tooltip="https://www.amazon.co.uk/dp/B0GQYM3S7R?psc=1"/>
+    <hyperlink ref="K45" r:id="rId219" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ahSAftNjL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L45" r:id="rId220" tooltip="https://www.amazon.co.uk/dp/B0GQYM3S7R"/>
+    <hyperlink ref="C46" r:id="rId221" tooltip="https://www.amazon.co.uk/dp/B0H1JBNL77"/>
     <hyperlink ref="G46" r:id="rId222" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M?psc=1"/>
-    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/719P6ABoSnL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.uk/dp/B0GGJB2H1M"/>
-    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B0GQYM3S7R"/>
+    <hyperlink ref="J46" r:id="rId223" tooltip="https://www.amazon.co.uk/dp/B0H1JBNL77?psc=1"/>
+    <hyperlink ref="K46" r:id="rId224" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71cBtcb4DrL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L46" r:id="rId225" tooltip="https://www.amazon.co.uk/dp/B0H1JBNL77"/>
+    <hyperlink ref="C47" r:id="rId226" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
     <hyperlink ref="G47" r:id="rId227" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0GQYM3S7R?psc=1"/>
-    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71ahSAftNjL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0GQYM3S7R"/>
-    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.uk/dp/B0H1JBNL77"/>
+    <hyperlink ref="J47" r:id="rId228" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1"/>
+    <hyperlink ref="K47" r:id="rId229" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61WO-PNCGuL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId230" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
+    <hyperlink ref="C48" r:id="rId231" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
     <hyperlink ref="G48" r:id="rId232" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B0H1JBNL77?psc=1"/>
-    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/71cBtcb4DrL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0H1JBNL77"/>
-    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
+    <hyperlink ref="J48" r:id="rId233" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1"/>
+    <hyperlink ref="K48" r:id="rId234" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId235" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
+    <hyperlink ref="C49" r:id="rId236" tooltip="https://www.amazon.co.uk/dp/B0HC816GR1"/>
     <hyperlink ref="G49" r:id="rId237" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5?psc=1"/>
-    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61WO-PNCGuL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0H6KDXVQ5"/>
-    <hyperlink ref="C50" r:id="rId241" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
-    <hyperlink ref="G50" r:id="rId242" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J50" r:id="rId243" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB?psc=1"/>
-    <hyperlink ref="K50" r:id="rId244" tooltip="https://images-eu.ssl-images-amazon.com/images/I/61faJrtabwL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId245" tooltip="https://www.amazon.co.uk/dp/B0H98GCFZB"/>
-    <hyperlink ref="C51" r:id="rId246" tooltip="https://www.amazon.co.uk/dp/B0HC816GR1"/>
-    <hyperlink ref="G51" r:id="rId247" tooltip="https://www.amazon.co.ukundefined"/>
-    <hyperlink ref="J51" r:id="rId248" tooltip="https://www.amazon.co.uk/dp/B0HC816GR1?psc=1"/>
-    <hyperlink ref="K51" r:id="rId249" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717QutrBkcL._AC_UL300_SR300,200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId250" tooltip="https://www.amazon.co.uk/dp/B0HC816GR1"/>
+    <hyperlink ref="J49" r:id="rId238" tooltip="https://www.amazon.co.uk/dp/B0HC816GR1?psc=1"/>
+    <hyperlink ref="K49" r:id="rId239" tooltip="https://images-eu.ssl-images-amazon.com/images/I/717QutrBkcL._AC_UL300_SR300,200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId240" tooltip="https://www.amazon.co.uk/dp/B0HC816GR1"/>
   </hyperlinks>
-  <drawing r:id="rId251"/>
+  <drawing r:id="rId241"/>
 </worksheet>
 </file>
 
